--- a/excel-files/MALABON/TANONG IS.xlsx
+++ b/excel-files/MALABON/TANONG IS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="511" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7F5398B-5B19-4EEF-B17C-EEC937F84AF0}"/>
+  <xr:revisionPtr revIDLastSave="616" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1692B0AD-29C8-4C5F-B677-ACAF929C8C39}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5560,8 +5560,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -12602,7 +12602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>25</v>
       </c>
@@ -13819,7 +13819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -14071,15 +14071,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L91" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L90 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110 X112:X127" xr:uid="{2292FEF1-041A-445F-8611-CF6A5C1BDA5B}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23028,12 +23031,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{9F669062-101E-4E48-8A5B-071463F73ECD}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/MALABON/TANONG IS.xlsx
+++ b/excel-files/MALABON/TANONG IS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="616" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1692B0AD-29C8-4C5F-B677-ACAF929C8C39}"/>
+  <xr:revisionPtr revIDLastSave="664" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1C67E80-F1B8-403C-B3C4-0BBB4FD7D89C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -428,7 +428,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,6 +498,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -759,6 +765,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3722,12 +3731,16 @@
       <c r="C11" s="1">
         <v>214</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="D11" s="1">
+        <v>180</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
       <c r="F11" s="5"/>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>214</v>
+        <v>34</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
@@ -3913,16 +3926,18 @@
       <c r="C21" s="1">
         <v>213</v>
       </c>
-      <c r="D21" s="1"/>
+      <c r="D21" s="46">
+        <v>360</v>
+      </c>
       <c r="E21" s="1"/>
       <c r="F21" s="5"/>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24" customHeight="1">
@@ -3935,16 +3950,18 @@
       <c r="C22" s="1">
         <v>213</v>
       </c>
-      <c r="D22" s="1"/>
+      <c r="D22" s="46">
+        <v>360</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="5"/>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="19.5">
@@ -3957,7 +3974,7 @@
       <c r="C23" s="1">
         <v>213</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="46"/>
       <c r="E23" s="1"/>
       <c r="F23" s="5"/>
       <c r="G23" s="3">
@@ -3979,7 +3996,7 @@
       <c r="C24" s="1">
         <v>213</v>
       </c>
-      <c r="D24" s="1"/>
+      <c r="D24" s="46"/>
       <c r="E24" s="1"/>
       <c r="F24" s="5"/>
       <c r="G24" s="3">
@@ -4001,16 +4018,18 @@
       <c r="C25" s="1">
         <v>213</v>
       </c>
-      <c r="D25" s="1"/>
+      <c r="D25" s="46">
+        <v>360</v>
+      </c>
       <c r="E25" s="1"/>
       <c r="F25" s="5"/>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33.75" customHeight="1">
@@ -4023,16 +4042,18 @@
       <c r="C26" s="1">
         <v>213</v>
       </c>
-      <c r="D26" s="1"/>
+      <c r="D26" s="46">
+        <v>360</v>
+      </c>
       <c r="E26" s="1"/>
       <c r="F26" s="5"/>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33.75" customHeight="1">
@@ -4045,16 +4066,18 @@
       <c r="C27" s="1">
         <v>213</v>
       </c>
-      <c r="D27" s="1"/>
+      <c r="D27" s="46">
+        <v>360</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="5"/>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27.75" customHeight="1">
@@ -4067,7 +4090,7 @@
       <c r="C28" s="1">
         <v>213</v>
       </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="46"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
@@ -4089,16 +4112,20 @@
       <c r="C29" s="1">
         <v>213</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="D29" s="46">
+        <v>360</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
       <c r="F29" s="5"/>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4121,16 +4148,20 @@
       <c r="C31" s="1">
         <v>199</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="D31" s="1">
+        <v>330</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2026</v>
+      </c>
       <c r="F31" s="5"/>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4231,16 +4262,20 @@
       <c r="C36" s="1">
         <v>199</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="D36" s="1">
+        <v>330</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
       <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4253,16 +4288,20 @@
       <c r="C37" s="1">
         <v>199</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="D37" s="1">
+        <v>330</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
       <c r="F37" s="5"/>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4275,16 +4314,20 @@
       <c r="C38" s="1">
         <v>199</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="D38" s="1">
+        <v>330</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
       <c r="F38" s="5"/>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4615,16 +4658,20 @@
       <c r="C54" s="10">
         <v>342</v>
       </c>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
+      <c r="D54" s="10">
+        <v>427</v>
+      </c>
+      <c r="E54" s="10">
+        <v>2026</v>
+      </c>
       <c r="F54" s="12"/>
       <c r="G54" s="3">
         <f t="shared" si="10"/>
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="H54" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="39" customHeight="1">
@@ -4665,16 +4712,18 @@
       <c r="C56" s="10">
         <v>342</v>
       </c>
-      <c r="D56" s="10"/>
+      <c r="D56" s="10">
+        <v>390</v>
+      </c>
       <c r="E56" s="10"/>
       <c r="F56" s="12"/>
       <c r="G56" s="3">
         <f t="shared" si="10"/>
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="H56" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="27.75" customHeight="1">
@@ -4687,16 +4736,18 @@
       <c r="C57" s="10">
         <v>342</v>
       </c>
-      <c r="D57" s="10"/>
+      <c r="D57" s="10">
+        <v>427</v>
+      </c>
       <c r="E57" s="10"/>
       <c r="F57" s="12"/>
       <c r="G57" s="3">
         <f t="shared" si="10"/>
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="H57" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="27.75" customHeight="1">
@@ -4709,16 +4760,18 @@
       <c r="C58" s="10">
         <v>342</v>
       </c>
-      <c r="D58" s="10"/>
+      <c r="D58" s="10">
+        <v>427</v>
+      </c>
       <c r="E58" s="10"/>
       <c r="F58" s="12"/>
       <c r="G58" s="3">
         <f t="shared" si="10"/>
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="H58" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="27.75" customHeight="1">
@@ -4767,16 +4820,18 @@
       <c r="C61" s="10">
         <v>380</v>
       </c>
-      <c r="D61" s="10"/>
+      <c r="D61" s="10">
+        <v>387</v>
+      </c>
       <c r="E61" s="10"/>
       <c r="F61" s="12"/>
       <c r="G61" s="3">
         <f t="shared" ref="G61:G69" si="12">IF((C61-D61)&lt;0,0,C61-D61)</f>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H61" s="4">
         <f t="shared" ref="H61:H69" si="13">IF((D61-C61)&lt;0,0,D61-C61)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="27.75" customHeight="1">
@@ -4789,16 +4844,18 @@
       <c r="C62" s="10">
         <v>380</v>
       </c>
-      <c r="D62" s="10"/>
+      <c r="D62" s="10">
+        <v>387</v>
+      </c>
       <c r="E62" s="10"/>
       <c r="F62" s="12"/>
       <c r="G62" s="3">
         <f t="shared" si="12"/>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H62" s="4">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="27.75" customHeight="1">
@@ -4889,16 +4946,22 @@
       <c r="C66" s="10">
         <v>380</v>
       </c>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="12"/>
+      <c r="D66" s="10">
+        <v>387</v>
+      </c>
+      <c r="E66" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="G66" s="3">
         <f t="shared" si="12"/>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="27.75" customHeight="1">
@@ -23031,14 +23094,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{9F669062-101E-4E48-8A5B-071463F73ECD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
